--- a/SPC_FINAL_EVIDENCE_AND_DIMENSIONS_20260825_103839.xlsx
+++ b/SPC_FINAL_EVIDENCE_AND_DIMENSIONS_20260825_103839.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uetpk-my.sharepoint.com/personal/adeel_munir_uet_edu_pk/Documents/Drive G/Data science coding/VSCode programming/Research_Paper_Integrated_Human_Digital_Strategic_Risk_Coordination_Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_B07DC4E7F30A26D564684E6F8C6ABE200B6A3371" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F1CDB3A-E550-4DFF-A92E-45AA438B673C}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="11_B07DC4E7F30A26D564684E6F8C6ABE200B6A3371" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20FB75FC-02DF-4E98-9C02-1BC48A9C4F81}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="11" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1904" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1903" uniqueCount="203">
   <si>
     <t>Participant</t>
   </si>
@@ -645,6 +645,9 @@
   </si>
   <si>
     <t>investment; resilience investment</t>
+  </si>
+  <si>
+    <t>High</t>
   </si>
 </sst>
 </file>
@@ -3233,22 +3236,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>42.3</v>
+        <v>88.5</v>
       </c>
       <c r="F2" t="s">
-        <v>146</v>
+        <v>202</v>
       </c>
       <c r="G2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -3256,22 +3259,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E3">
-        <v>30.8</v>
+        <v>80.8</v>
       </c>
       <c r="F3" t="s">
-        <v>146</v>
+        <v>202</v>
       </c>
       <c r="G3" t="s">
-        <v>102</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -3279,22 +3282,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E4">
-        <v>15.4</v>
+        <v>42.3</v>
       </c>
       <c r="F4" t="s">
         <v>147</v>
       </c>
       <c r="G4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -3302,22 +3305,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E5">
-        <v>11.5</v>
+        <v>34.6</v>
       </c>
       <c r="F5" t="s">
         <v>147</v>
       </c>
       <c r="G5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -3325,22 +3328,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C6">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E6">
-        <v>11.5</v>
+        <v>30.8</v>
       </c>
       <c r="F6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G6" t="s">
-        <v>197</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -3348,22 +3351,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>166</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
+        <v>189</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E7">
-        <v>7.7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>147</v>
+        <v>23.1</v>
       </c>
       <c r="G7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -3371,22 +3368,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8">
-        <v>7.7</v>
+        <v>11.5</v>
       </c>
       <c r="F8" t="s">
         <v>147</v>
       </c>
       <c r="G8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -3394,22 +3391,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>3.8</v>
+        <v>7.7</v>
       </c>
       <c r="F9" t="s">
         <v>147</v>
       </c>
       <c r="G9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -3417,10 +3414,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -3432,7 +3429,7 @@
         <v>147</v>
       </c>
       <c r="G10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
